--- a/kits/security-questionnaire/samples/output/cobalt-ridge-supplier-security-questionnaire_DRAFT.xlsx
+++ b/kits/security-questionnaire/samples/output/cobalt-ridge-supplier-security-questionnaire_DRAFT.xlsx
@@ -2476,7 +2476,7 @@
       </c>
       <c r="O9" s="14" t="inlineStr">
         <is>
-          <t>idp, ident, customeruser, provid, login</t>
+          <t>ident, idp, customeruser, provid, login</t>
         </is>
       </c>
       <c r="P9" s="17" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="O13" s="14" t="inlineStr">
         <is>
-          <t>anti, malwar, endpoint, antimalware, detect, softwar</t>
+          <t>anti, endpoint, malwar, antimalware, detect, softwar</t>
         </is>
       </c>
       <c r="P13" s="17" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="O16" s="14" t="inlineStr">
         <is>
-          <t>certif, iso, iso27001, hold, 27001</t>
+          <t>certif, 27001, hold, iso, iso27001</t>
         </is>
       </c>
       <c r="P16" s="17" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="O26" s="14" t="inlineStr">
         <is>
-          <t>sever, fix, vulner, timeframe</t>
+          <t>fix, sever, vulner, timeframe</t>
         </is>
       </c>
       <c r="P26" s="17" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="O33" s="14" t="inlineStr">
         <is>
-          <t>complet, awar, securitytraining, train, staff, secur</t>
+          <t>awar, complet, securitytraining, train, staff, secur</t>
         </is>
       </c>
       <c r="P33" s="17" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="O37" s="14" t="inlineStr">
         <is>
-          <t>file, encryptrest, databas, store, encrypt, data</t>
+          <t>file, databas, encryptrest, store, encrypt, data</t>
         </is>
       </c>
       <c r="P37" s="17" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="O38" s="14" t="inlineStr">
         <is>
-          <t>artifici, machin, intellig, learn, model, ai</t>
+          <t>artifici, intellig, learn, machin, model, ai</t>
         </is>
       </c>
       <c r="P38" s="17" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="O43" s="14" t="inlineStr">
         <is>
-          <t>static, depscan, autom, analys, sast, depend</t>
+          <t>analys, autom, depscan, static, sast, depend</t>
         </is>
       </c>
       <c r="P43" s="17" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="O44" s="14" t="inlineStr">
         <is>
-          <t>non, product, nonprod, separate, environ, prod</t>
+          <t>non, nonprod, product, separate, environ, prod</t>
         </is>
       </c>
       <c r="P44" s="17" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="O46" s="14" t="inlineStr">
         <is>
-          <t>object, time, rpo, point, recov, servic</t>
+          <t>object, rpo, time, point, recov, servic</t>
         </is>
       </c>
       <c r="P46" s="17" t="inlineStr">
